--- a/app_creator/venue_dimension/venues_final.xlsx
+++ b/app_creator/venue_dimension/venues_final.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\git-younghyun\analysis_repo\app_creator\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\younghyun\git_younghyun\analysis_repo\app_creator\venue_dimension\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18BB2421-66E6-4850-A1E0-94A4DC7AD077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2068721C-AF33-44D1-97D3-5113C47AE1A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="135">
   <si>
     <t>venue_confirm</t>
   </si>
@@ -467,6 +467,10 @@
   </si>
   <si>
     <t>활기체육공원축구장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고양시</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -815,12 +819,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C79"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="27.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -831,7 +835,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -842,7 +846,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -853,7 +857,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -864,7 +868,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -875,7 +879,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -886,7 +890,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -897,7 +901,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -908,7 +912,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -919,7 +923,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -930,7 +934,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -938,7 +942,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -949,7 +953,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -960,7 +964,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -971,7 +975,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -982,7 +986,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -993,7 +997,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A17" t="s">
         <v>23</v>
       </c>
@@ -1004,7 +1008,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -1015,7 +1019,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -1026,7 +1030,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A20" t="s">
         <v>26</v>
       </c>
@@ -1037,7 +1041,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A21" t="s">
         <v>27</v>
       </c>
@@ -1048,7 +1052,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A22" t="s">
         <v>28</v>
       </c>
@@ -1059,7 +1063,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A23" t="s">
         <v>29</v>
       </c>
@@ -1070,7 +1074,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -1081,7 +1085,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -1092,7 +1096,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -1103,7 +1107,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A27" t="s">
         <v>34</v>
       </c>
@@ -1114,7 +1118,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A28" t="s">
         <v>35</v>
       </c>
@@ -1125,7 +1129,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A29" t="s">
         <v>36</v>
       </c>
@@ -1136,7 +1140,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A30" t="s">
         <v>37</v>
       </c>
@@ -1147,7 +1151,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A31" t="s">
         <v>38</v>
       </c>
@@ -1158,7 +1162,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A32" t="s">
         <v>39</v>
       </c>
@@ -1169,7 +1173,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A33" t="s">
         <v>40</v>
       </c>
@@ -1180,7 +1184,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A34" t="s">
         <v>41</v>
       </c>
@@ -1188,7 +1192,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A35" t="s">
         <v>42</v>
       </c>
@@ -1199,7 +1203,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A36" t="s">
         <v>43</v>
       </c>
@@ -1210,7 +1214,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A37" t="s">
         <v>44</v>
       </c>
@@ -1221,7 +1225,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A38" t="s">
         <v>45</v>
       </c>
@@ -1232,7 +1236,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A39" t="s">
         <v>46</v>
       </c>
@@ -1243,7 +1247,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A40" t="s">
         <v>47</v>
       </c>
@@ -1254,7 +1258,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A41" t="s">
         <v>48</v>
       </c>
@@ -1265,7 +1269,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A42" t="s">
         <v>49</v>
       </c>
@@ -1276,7 +1280,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A43" t="s">
         <v>50</v>
       </c>
@@ -1287,7 +1291,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A44" t="s">
         <v>51</v>
       </c>
@@ -1298,7 +1302,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A45" t="s">
         <v>52</v>
       </c>
@@ -1309,7 +1313,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A46" t="s">
         <v>53</v>
       </c>
@@ -1320,7 +1324,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A47" t="s">
         <v>54</v>
       </c>
@@ -1331,7 +1335,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A48" t="s">
         <v>55</v>
       </c>
@@ -1342,7 +1346,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A49" t="s">
         <v>56</v>
       </c>
@@ -1353,7 +1357,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A50" t="s">
         <v>57</v>
       </c>
@@ -1364,7 +1368,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A51" t="s">
         <v>58</v>
       </c>
@@ -1375,7 +1379,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A52" t="s">
         <v>59</v>
       </c>
@@ -1386,18 +1390,18 @@
         <v>117</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A53" t="s">
         <v>60</v>
       </c>
       <c r="B53" t="s">
-        <v>20</v>
+        <v>134</v>
       </c>
       <c r="C53" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A54" t="s">
         <v>61</v>
       </c>
@@ -1408,7 +1412,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A55" t="s">
         <v>62</v>
       </c>
@@ -1419,7 +1423,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A56" t="s">
         <v>63</v>
       </c>
@@ -1430,7 +1434,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A57" t="s">
         <v>64</v>
       </c>
@@ -1441,7 +1445,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A58" t="s">
         <v>65</v>
       </c>
@@ -1452,7 +1456,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A59" t="s">
         <v>66</v>
       </c>
@@ -1463,7 +1467,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A60" t="s">
         <v>67</v>
       </c>
@@ -1474,7 +1478,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A61" t="s">
         <v>68</v>
       </c>
@@ -1485,7 +1489,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A62" t="s">
         <v>69</v>
       </c>
@@ -1496,7 +1500,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A63" t="s">
         <v>70</v>
       </c>
@@ -1507,7 +1511,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A64" t="s">
         <v>71</v>
       </c>
@@ -1518,7 +1522,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A65" t="s">
         <v>72</v>
       </c>
@@ -1529,7 +1533,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A66" t="s">
         <v>73</v>
       </c>
@@ -1540,7 +1544,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A67" t="s">
         <v>74</v>
       </c>
@@ -1551,7 +1555,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A68" t="s">
         <v>75</v>
       </c>
@@ -1562,7 +1566,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A69" t="s">
         <v>76</v>
       </c>
@@ -1573,7 +1577,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A70" t="s">
         <v>77</v>
       </c>
@@ -1584,7 +1588,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A71" t="s">
         <v>78</v>
       </c>
@@ -1595,7 +1599,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A72" t="s">
         <v>79</v>
       </c>
@@ -1606,7 +1610,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A73" t="s">
         <v>80</v>
       </c>
@@ -1617,7 +1621,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A74" t="s">
         <v>81</v>
       </c>
@@ -1628,7 +1632,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A75" t="s">
         <v>82</v>
       </c>
@@ -1639,7 +1643,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A76" t="s">
         <v>83</v>
       </c>
@@ -1650,7 +1654,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A77" t="s">
         <v>84</v>
       </c>
@@ -1661,7 +1665,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A78" t="s">
         <v>85</v>
       </c>
@@ -1672,7 +1676,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A79" t="s">
         <v>86</v>
       </c>
@@ -1686,5 +1690,6 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>